--- a/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="127">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Mapping du modèle métier Patient : CDA et FHIR</t>
+    <t>Mapping du modèle métier Patient/CDA/FHIR</t>
   </si>
   <si>
     <t>Title</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T13:18:22+00:00</t>
+    <t>2025-03-14T15:47:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +82,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping du modèle métier Patient entre CDA et FHIR.</t>
+    <t>Ce ConceptMap présente deux groupes de mapping : 
+ - Groupe Mapping 1 : entre le modèle métier du Patient/Usager et l'élément CDA recordTarget
+ - Groupe Mapping 2 : entre l'élément CDA recordTarget et FrPatientDocument en FHIR</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -154,12 +156,15 @@
     <t>Patient.personnePhysique.nomsPrenoms.noms.nomNaissance</t>
   </si>
   <si>
-    <t>PrecordTarget.patientRole.patient.name.family</t>
+    <t>PrecordTarget.patientRole.patient.name.family@qualifier='BR'</t>
   </si>
   <si>
     <t>Patient.personnePhysique.nomsPrenoms.noms.nomUtilise</t>
   </si>
   <si>
+    <t>recordTarget.patientRole.patient.name.family@qualifier='CL'</t>
+  </si>
+  <si>
     <t>Patient.personnePhysique.nomsPrenoms.prenoms</t>
   </si>
   <si>
@@ -172,9 +177,15 @@
     <t>Patient.personnePhysique.nomsPrenoms.prenoms.premierPrenom</t>
   </si>
   <si>
+    <t>recordTarget.patientRole.patient.name.given@qualifier='BR'</t>
+  </si>
+  <si>
     <t>Patient.personnePhysique.nomsPrenoms.prenoms.prenomUtilise</t>
   </si>
   <si>
+    <t>recordTarget.patientRole.patient.name.given@qualifier='CL'</t>
+  </si>
+  <si>
     <t>Patient.sexe</t>
   </si>
   <si>
@@ -310,6 +321,9 @@
     <t>Patient.name.family</t>
   </si>
   <si>
+    <t>recordTarget.patientRole.patient.name.family@qualifier='BR'</t>
+  </si>
+  <si>
     <t>Patient.name:officialname.family</t>
   </si>
   <si>
@@ -346,7 +360,7 @@
     <t>Patient.multipleBirthInteger</t>
   </si>
   <si>
-    <t>Patient.contact.relationship:Role</t>
+    <t>Patient.contact.relationship:Role='GUARD'</t>
   </si>
   <si>
     <t>Patient.contact.address</t>
@@ -775,306 +789,306 @@
         <v>33</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E33" s="2"/>
     </row>
@@ -1116,7 +1130,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>30</v>
@@ -1124,7 +1138,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -1144,7 +1158,7 @@
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -1157,7 +1171,7 @@
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1170,7 +1184,7 @@
         <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -1183,7 +1197,7 @@
         <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -1196,332 +1210,332 @@
         <v>33</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E33" s="2"/>
     </row>

--- a/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
   <si>
     <t>Ce ConceptMap présente deux groupes de mapping : 
  - Groupe Mapping 1 : entre le modèle métier du Patient/Usager et l'élément CDA recordTarget
- - Groupe Mapping 2 : entre l'élément CDA recordTarget et FrPatientDocument en FHIR</t>
+ - Groupe Mapping 2 : entre l'élément CDA recordTarget et le profil FHIR FrPatientDocument</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
